--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_03_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_03_20_Cau.xlsx
@@ -938,7 +938,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm tra dependency và cách merge trước khi chạy song song.</t>
+          <t>Thiết kế fan-out/fan-in song song đúng: Chạy ba phân tích song song nếu cùng nhận đầu vào chuẩn hóa (a), Định nghĩa schema đầu ra chung cho bộ tổng hợp (b), và Quy định xử lý khi một nhánh hết thời gian chờ (d).</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>240000</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
@@ -972,7 +976,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nhân số báo cáo, số nhánh và token của mỗi nhánh.</t>
+          <t>Tổng số nhánh = 40 báo cáo × 3 nhánh/báo cáo = 120 nhánh. Với mỗi nhánh dùng 2.000 token, tổng số token là 120 × 2.000 = 240.000 token.</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1100,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo luồng đầu ra → tiêu chí → phản hồi → sửa lại.</t>
+          <t>Vòng lặp Evaluator–Optimizer: Bộ sinh (Generator) tạo bản nháp (o3) -&gt; Bộ đánh giá (Evaluator) chấm theo tiêu chí (o2) -&gt; Bộ đánh giá trả phản hồi cụ thể cho các tiêu chí chưa đạt (o4) -&gt; Bộ sinh sửa đầu ra theo phản hồi (o1).</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1251,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xếp theo việc ai thực hiện tác động bên ngoài và bằng chứng cần có.</t>
+          <t>Lộ trình tăng mức tự chủ an toàn từ thấp đến cao: Gợi ý cho người dùng tự thực hiện (o2) -&gt; Tạo nháp bắt buộc người duyệt (Human-in-the-loop) (o3) -&gt; Tự động hóa có giám sát và can thiệp (o1).</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1303,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ tăng một pha, không xóa các kiểm soát đã tạo ra bằng chứng.</t>
+          <t>Hệ thống soạn email nội bộ rủi ro thấp đã qua 2.000 test case tốt. Bước tiếp theo hợp lý là chuyển sang tự động hóa có giám sát trong phạm vi giới hạn, vẫn giữ kiểm tra chính sách và nút dừng khẩn cấp.</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1433,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hiển thị thứ người dùng cần để truy lại nguồn và biết giới hạn của kết luận.</t>
+          <t>Để bảo đảm tính minh bạch khi trả lời chính sách, hệ thống cần: Liên kết/tên tài liệu và đoạn liên quan (a), Ngày hiệu lực hoặc thời điểm truy xuất (b), và Cảnh báo rõ khi hai nguồn có nội dung mâu thuẫn (c).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_03_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_03_20_Cau.xlsx
@@ -626,10 +626,21 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đặt từng câu “phải luôn đúng” thành một phép kiểm tra trước khi ghi nhận quyết định.
-Phân tích theo nguyên lý thiết kế: Đặt từng câu “phải luôn đúng” thành một phép kiểm tra trước khi ghi nhận quyết định.</t>
+- Phân việc đúng bản chất AI và Luật (1.0 điểm): Giao AI đọc mô tả tự nhiên trích JSON; giao code tất định kiểm tra các điều kiện bất biến.
+- Thiết kế đủ 3 điểm kiểm soát bất biến (2.0 điểm): Nêu rõ code/logic kiểm tra tổng bằng chi tiết, người duyệt khác người nộp và khoản &gt; 50 triệu bắt buộc có CFO duyệt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế phân việc và các điểm kiểm soát cho quy trình duyệt chi phí:
+1. Phân việc hợp lý giữa AI xác suất và Logic tất định:
+- Phần giao cho AI (LLM Probabilistic Task): Đọc và trích xuất thông tin phi cấu trúc từ mô tả hóa đơn/chứng từ viết tự do (tên nhà cung cấp, loại chi phí, lý do công tác) chuyển thành đối tượng JSON có cấu trúc.
+- Phần giao cho Mã nguồn tất định (Deterministic Code / Assertions): Kiểm tra toàn bộ các điều kiện bất biến (Invariants) bằng code Python/SQL, tuyệt đối không dùng LLM để thẩm định các quy tắc này.
+2. Ba điểm kiểm soát bất biến (Invariant Control Gates):
+- Điểm kiểm soát 1 (Toán học số học): `assert round(total_amount, 2) == round(sum(item.amount for item in line_items), 2)`. Nếu lệch dù chỉ 1 đồng, tự động từ chối và báo lỗi tính toán.
+- Điểm kiểm soát 2 (Tách biệt quyền hạn - Segregation of Duties): `assert approver_id != submitter_id`. Nếu trùng lặp định danh, hệ thống tự động chặn và ném ngoại lệ xung đột lợi ích.
+- Điểm kiểm soát 3 (Phân cấp thẩm quyền chi tiêu): `if total_amount &gt; 50_000_000: assert 'CFO' in approver_roles`. Nếu số tiền trên 50 triệu mà không có phê duyệt của CFO, hệ thống khóa không cho giải ngân.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc 'Deterministic Invariants Guarding Probabilistic Outputs': Các quy tắc nghiệp vụ tài chính và tuân thủ pháp lý là các bất biến tuyệt đối (Hard Invariants). Mọi đầu ra do LLM trích xuất bắt buộc phải đi qua các cổng kiểm tra xác thực (Validation Gates) bằng mã nguồn tất định trước khi được ghi nhận vào sổ cái kế toán.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Meyer, B. (1992). Applying 'Design by Contract'. IEEE Computer (https://www.eiffel.com/values/design-by-contract/); Google Cloud Architecture - Financial Processing AI Patterns (https://cloud.google.com/architecture)</t>
         </is>
       </c>
     </row>
@@ -764,10 +775,24 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết hợp đồng đầu vào/đầu ra của từng bước, rồi đặt điểm kiểm soát trước khi truyền kết quả sang bước sau.
-Phân tích theo nguyên lý thiết kế: Viết hợp đồng đầu vào/đầu ra của từng bước, rồi đặt điểm kiểm soát trước khi truyền kết quả sang bước sau.</t>
+- Hợp đồng đầu vào/đầu ra từng bước rõ ràng (1.0 điểm): Định nghĩa chuẩn xác input/output cho phân loại, trích xuất và tóm tắt rủi ro.
+- Điểm kiểm soát từ chối/thử lại (1.0 điểm): Đặt validator giữa các bước để kiểm tra loại hợp đồng và độ đầy đủ của trường bắt buộc.
+- Phân tích phụ thuộc và đánh đổi độ trễ vs kiểm soát (1.0 điểm): Phân tích rõ việc chấp nhận tăng latency gấp 3 để đạt khả năng kiểm soát chất lượng và debug cao.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế chuỗi 3 lượt gọi có đầu vào / đầu ra rõ ràng:
+- Bước 1 (Phân loại): Đầu vào = Văn bản hợp đồng thô. Đầu ra = JSON `{contract_type: 'NDA' | 'Vendor' | 'Employment'}`.
+- Bước 2 (Trích xuất có điều kiện): Đầu vào = Văn bản hợp đồng + `contract_type`. Đầu ra = JSON chứa các trường điều khoản tương ứng (bảo mật, thanh toán, phạt vi phạm, hiệu lực).
+- Bước 3 (Tóm tắt rủi ro): Đầu vào = Dữ liệu các điều khoản đã trích xuất hợp lệ. Đầu ra = Báo cáo phân tích rủi ro có cấu trúc kèm điểm cảnh báo.
+2. Điểm kiểm soát chất lượng (Quality Checkpoints):
+- Giữa Bước 1 và 2: Kiểm tra `contract_type` phải thuộc danh mục hợp lệ. Nếu là 'Khác/Không xác định', dừng chuỗi và chuyển cho chuyên viên pháp chế rà soát thủ công.
+- Giữa Bước 2 và 3: Sử dụng JSON Schema Validator (code tất định) để kiểm tra xem đã trích xuất đầy đủ 100% các trường bắt buộc hay chưa. Nếu thiếu trường, tự động kích hoạt thử lại (Retry) với prompt chuyên biệt trích xuất riêng trường bị thiếu; nếu thử lại thất bại thì đánh dấu cờ cảnh báo hồ sơ khiếm khuyết.
+3. Sự phụ thuộc và đánh đổi (Dependencies &amp; Trade-offs):
+- Sự phụ thuộc: Bước sau phụ thuộc nghiêm ngặt vào dữ liệu của bước trước (Sequential Pipeline).
+- Đánh đổi: Tăng độ trễ tổng thể (Latency tăng gấp 3 do chạy nối tiếp qua 3 lượt gọi LLM) để đổi lấy khả năng kiểm soát chặt chẽ từng chặng (Granular Controllability), dễ dàng gỡ lỗi (debuggability) và ngăn chặn ảo giác tích lũy dây chuyền.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mẫu hình Prompt Chaining (Chuỗi lời nhắc) chia nhỏ bài toán lớn thành các bước con tuần tự. Việc chèn các cổng kiểm soát schema tất định giữa các bước ngăn ngừa hiện tượng 'Garbage In, Garbage Out' lan truyền trong các đường ống xử lý ngôn ngữ tự nhiên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Claude Prompt Engineering Guide - Chaining Prompts (https://docs.anthropic.com/en/docs/build-with-claude/prompt-engineering); LangChain LCEL Chains.</t>
         </is>
       </c>
     </row>
@@ -801,10 +826,24 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hãy giữ lại trạng thái hồ sơ và trường đầu vào; đừng để lỗi một lượt biến thành quyết định không rõ nguồn.
-Phân tích theo nguyên lý thiết kế: Hãy giữ lại trạng thái hồ sơ và trường đầu vào; đừng để lỗi một lượt biến thành quyết định không rõ nguồn.</t>
+- Phản biện sâu sắc thiết kế monolithic (1.0 điểm): Chỉ ra lỗi quá tải nhận thức, thiếu truy vết bằng chứng và lỗi all-or-nothing khi fail.
+- Thiết kế chuỗi 3 bước kèm điểm kiểm soát &amp; đường lui (1.0 điểm): Trình bày rõ bước trích xuất (early exit nếu thiếu), đối chiếu bằng chứng và tổng hợp quyết định.
+- Phân tích đánh đổi độ trễ (1.0 điểm): Nêu rõ việc chấp nhận tăng latency nối tiếp để đổi lại tính giải trình, minh bạch và khả năng ngắt sớm.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phản biện thiết kế một lượt gọi duy nhất (Single-call monolithic design):
+Thiết kế 'gộp tất cả làm một' vi phạm nguyên tắc phân tách trách nhiệm (Separation of Concerns). Khi giao cho LLM vừa kiểm tra, vừa phán xét, vừa giải thích trong một prompt: (1) Mô hình dễ bị quá tải nhận thức dẫn đến ảo giác và bỏ qua các trường dữ liệu thiếu; (2) Thiếu khả năng truy vết nguồn gốc (không thể biết quyết định dựa trên bằng chứng nào trong hồ sơ); (3) Thiếu tính co giãn khi lỗi (All-or-nothing failure) — nếu xảy ra lỗi mạng hoặc lỗi định dạng ở cuối, toàn bộ kết quả bị hủy và phải chạy lại từ đầu rất tốn kém.
+2. Chuyển đổi thành chuỗi 3 bước chuẩn mực:
+- Bước 1: [Trích xuất &amp; Kiểm tra tính đầy đủ - Extraction &amp; Schema Validation]
+  + Input: Hồ sơ ứng viên thô. Output: JSON chứa các trường chuẩn hóa. Điểm kiểm soát: Code kiểm tra đủ trường bắt buộc. Đường lui: Nếu thiếu, lập tức trả trạng thái 'Hồ sơ thiếu thông tin' và gửi thông báo yêu cầu bổ sung.
+- Bước 2: [Đối chiếu tiêu chuẩn - Evidence Evaluation]
+  + Input: JSON hồ sơ chuẩn + Bộ tiêu chí đánh giá. Output: Bảng đối soát từng tiêu chí (Đạt/Không đạt) kèm trích dẫn nguyên văn bằng chứng. Điểm kiểm soát: Kiểm tra mọi tiêu chí đều có bằng chứng trích dẫn.
+- Bước 3: [Tổng hợp quyết định &amp; Tạo giải trình - Decision &amp; Explanation]
+  + Input: Bảng đối soát từ Bước 2. Output: Quyết định chung cuộc và thư giải thích minh bạch.
+3. Đánh đổi về độ trễ: Chấp nhận độ trễ tăng từ ~2 giây lên ~5-6 giây (do chạy 3 lượt nối tiếp) để đổi lại tính minh bạch tuyệt đối, khả năng kiểm toán 100% và giảm 90% chi phí tính toán khi hồ sơ thiếu trường bị ngắt sớm ngay từ Bước 1.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tái cấu trúc từ Monolithic Prompt sang Micro-Prompts. Bằng cách đưa khâu kiểm tra trường bắt buộc lên bước đầu (Early Exit / Fail-Fast), hệ thống tiết kiệm tài nguyên và đảm bảo mỗi quyết định Đạt/Không đạt đều có bằng chứng cụ thể neo đậu trong dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents: Prompt Chaining Workflow (https://www.anthropic.com/research/building-effective-agents); Martin Fowler - Monolith to Microservices Pattern (https://martinfowler.com/articles/monolith-to-microservices.html)</t>
         </is>
       </c>
     </row>
@@ -840,10 +879,28 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ưu tiên hành động và rủi ro trước, rồi mới tối ưu chi phí.
-Phân tích theo nguyên lý thiết kế: Ưu tiên hành động và rủi ro trước, rồi mới tối ưu chi phí.</t>
+- Thiết kế đủ 3 nhánh xử lý kèm ngưỡng điều kiện (1.5 điểm): Phân nhánh báo mất thẻ (ưu tiên rủi ro cao/khóa thẻ ngay), đổi địa chỉ (kèm điều kiện trạng thái đơn/OTP) và tra đơn hàng.
+- Phương án dự phòng và phân tích hậu quả chuyển nhầm (1.5 điểm): Nêu fallback menu nút bấm và phân tích sâu sắc hậu quả tài chính khi chuyển nhầm nhánh mất thẻ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế các nhánh xử lý, ngưỡng và phương án dự phòng:
+- Bộ định tuyến (Intent &amp; Risk Router) sử dụng phân tích đa tín hiệu: Phân loại ý định kết hợp kiểm tra từ khóa rủi ro khẩn cấp và trạng thái đơn hàng.
++ Nhánh 1 (Khẩn cấp - Rủi ro cao): 'Báo mất thẻ thanh toán'
+  * Ngưỡng kích hoạt: Bất kỳ khi nào phát hiện từ khóa rủi ro liên quan đến mất thẻ/gian lận hoặc cờ rủi ro `risk_flag == HIGH` (không phụ thuộc vào độ tin cậy của intent).
+  * Xử lý: Lập tức gọi API khóa thẻ tạm thời tất định và chuyển ngay cuộc gọi/chat cho chuyên viên an ninh tài chính 24/7 (Human Escalate). Không bao giờ để LLM trả lời tự do.
++ Nhánh 2 (Tác vụ thay đổi trạng thái có điều kiện): 'Thay đổi địa chỉ trước khi giao'
+  * Ngưỡng kích hoạt: Intent confidence &gt;= 0,85 VÀ `order_status == 'PENDING_DISPATCH'` (đơn hàng chưa giao cho shipper).
+  * Xử lý: Yêu cầu xác thực OTP của khách hàng -&gt; Cho phép sửa địa chỉ trong DB -&gt; Gửi xác nhận. Nếu đơn đã ở trạng thái 'IN_TRANSIT', tự động từ chối và hướng dẫn liên hệ tổng đài.
++ Nhánh 3 (Tác vụ đọc thông tin an toàn): 'Tra trạng thái đơn hàng'
+  * Ngưỡng kích hoạt: Intent confidence &gt;= 0,80.
+  * Xử lý: Gọi API tra cứu trạng thái và dùng template phản hồi nhanh cho khách.
+- Phương án dự phòng (Fallback): Nếu độ tin cậy ý định &lt; 0,80 hoặc tín hiệu mơ hồ, bot hiển thị menu chọn nhanh 3 nút bấm tương ứng trên giao diện.
+2. Hậu quả khi chuyển nhầm nhánh:
+- Chuyển nhầm từ 'Báo mất thẻ' sang 'Tra đơn': Thẻ của khách hàng không được khóa kịp thời, dẫn đến rủi ro phát sinh giao dịch gian lận tài chính hàng chục triệu đồng và trách nhiệm pháp lý nghiêm trọng.
+- Chuyển nhầm từ 'Đổi địa chỉ' sang nhánh khác: Hàng bị giao sai địa chỉ cũ, phát sinh chi phí hoàn hàng và làm mất lòng tin của khách hàng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mẫu hình Routing Pattern trong kiến trúc Agent tuân thủ nguyên tắc 'Ưu tiên Rủi ro trước Chi phí' (Safety-First Routing). Các sự kiện an ninh và thay đổi trạng thái tài sản phải được phân luồng xử lý với các chốt kiểm tra nghiệp vụ cứng, tuyệt đối không áp dụng cùng một cơ chế đối xử cho các tác vụ có mức độ thiệt hại chênh lệch nhau.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents: Routing Workflow (https://www.anthropic.com/research/building-effective-agents); Google SRE - Risk-Based Traffic Routing (https://sre.google/sre-book/)</t>
         </is>
       </c>
     </row>
@@ -877,10 +934,22 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Thêm một lớp ‘không chắc chắn’ trước khi tối ưu các nhánh xử lý.
-Phân tích theo nguyên lý thiết kế: Thêm một lớp ‘không chắc chắn’ trước khi tối ưu các nhánh xử lý.</t>
+- Thiết kế các nhánh phân luồng và lớp không chắc chắn (1.5 điểm): Phân luồng đúng FAQ, Reset mật khẩu (link bảo mật), Khiếu nại (chuyển người) và lớp đệm Disambiguation khi confidence thấp.
+- Nêu rõ rủi ro chuyển nhầm và phương án dự phòng (1.5 điểm): Phân tích hậu quả khách hàng giận dữ khi khiếu nại bị chuyển nhầm sang FAQ và cung cấp nút thoát (Escape Hatch) gặp nhân viên.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế các nhánh xử lý theo mức độ rủi ro và độ tin cậy:
+- Nhánh 1 (FAQ - Rủi ro thấp): Ngưỡng tin cậy &gt;= 0,80 -&gt; Tự động truy xuất kho tri thức RAG và trả lời tức thì cho khách hàng.
+- Nhánh 2 (Đặt lại mật khẩu - Rủi ro bảo mật trung bình): Ngưỡng tin cậy &gt;= 0,85 -&gt; Tuyệt đối không cho LLM tự cấp mật khẩu; hệ thống chỉ tự động gửi đường link đặt lại mật khẩu bảo mật (secure reset token) về email/SĐT đã đăng ký của khách hàng.
+- Nhánh 3 (Khiếu nại tài chính - Rủi ro cao): Bất kể điểm tin cậy -&gt; Tự động tạo ticket phân loại ưu tiên cao, thu thập mã giao dịch và chuyển thẳng cho nhân viên hỗ trợ chuyên trách xử lý.
+- Nhánh 4 (Lớp Không chắc chắn - Uncertainty / Disambiguation Fallback): Khi độ tin cậy của router rơi vào vùng mấp mé hoặc thấp (&lt; 0,80), hệ thống KHÔNG ĐOÁN MÒ mà kích hoạt phản hồi làm rõ với 3 nút bấm lựa chọn trực tiếp: '[1] Hỏi đáp thông tin', '[2] Quên mật khẩu', '[3] Khiếu nại giao dịch'.
+2. Rủi ro khi chuyển nhầm nhánh:
+- Chuyển nhầm 'Khiếu nại tài chính' sang 'FAQ': Bot trả lời chung chung giáo điều trong khi khách hàng đang bức xúc về việc bị trừ tiền oan, đẩy sự bức xúc lên cao trào và dẫn đến nguy cơ khiếu kiện truyền thông.
+- Chuyển nhầm 'Đặt lại mật khẩu' sang 'FAQ': Làm lộ hướng dẫn bảo mật không đúng bối cảnh hoặc làm gián đoạn quyền truy cập tài khoản của người dùng.
+3. Phương án dự phòng: Nút bấm 'Gặp nhân viên hỗ trợ' luôn hiển thị cố định ở mọi nhánh để khách hàng có thể thoát khỏi bot bất kỳ lúc nào (Escape Hatch).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: 'Uncertainty-Aware Routing'. Một bộ định tuyến thông minh không phải là bộ định tuyến luôn cố gắng ra quyết định phân loại, mà là bộ định tuyến biết khi nào mình 'không chắc chắn' để dừng lại, chủ động làm rõ ý định hoặc kích hoạt lối thoát khẩn cấp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nielsen Norman Group - Error Prevention in AI Interfaces (https://www.nngroup.com/articles/error-prevention-ai/); Anthropic - Routing Pattern Guidelines (https://www.anthropic.com/research/building-effective-agents)</t>
         </is>
       </c>
     </row>
@@ -1009,10 +1078,29 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Định nghĩa hợp đồng đầu vào/đầu ra và điều kiện dừng trước khi tăng số worker.
-Phân tích theo nguyên lý thiết kế: Định nghĩa hợp đồng đầu vào/đầu ra và điều kiện dừng trước khi tăng số worker.</t>
+- Sinh và giới hạn worker chuẩn mực (1.0 điểm): Nêu rõ việc Orchestrator tìm kiếm sơ bộ và đặt trần tối đa (ví dụ 8 worker) có hàng đợi ưu tiên.
+- Hợp đồng đầu vào/đầu ra JSON rõ ràng (1.0 điểm): Định nghĩa schema cụ thể cho worker gồm tên đối thủ, tính năng, giá và mảng trích dẫn nguồn.
+- Loại trùng, tổng hợp mâu thuẫn, ngân sách và xử lý lỗi (1.0 điểm): Trình bày đủ cách xử lý thông tin mâu thuẫn, ngân sách token/thời gian và dung sai lỗi từng phần.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế mô hình Orchestrator–Workers để lập hồ sơ cạnh tranh thị trường mới:
+1. Cách sinh và giới hạn nhiệm vụ con (Subtask Generation &amp; Bounds):
+- Orchestrator nhận chủ đề thị trường mới, thực hiện lượt tìm kiếm tổng quan đầu tiên để xác định danh sách các đối thủ tiềm năng sơ bộ.
+- Giới hạn số lượng worker (Concurrency Cap): Thiết lập ngưỡng cứng tối đa không quá 8 worker song song (đại diện cho top 8 đối thủ đáng chú ý nhất). Nếu phát hiện thêm đối thủ, Orchestrator đưa vào hàng đợi ưu tiên thay vì sinh worker không giới hạn.
+2. Hợp đồng đầu vào / đầu ra của Worker (Worker Interface Contract):
+- Input Contract: JSON `{competitor_name: str, domain_url: str, research_aspects: ['pricing', 'core_features', 'target_customers']}`.
+- Output Contract: JSON nghiêm ngặt tuân thủ schema:
+  `{competitor_name: str, founded_year: int, pricing_model: str, key_features: list[str], strengths: list[str], weaknesses: list[str], sources: list[str]}`.
+3. Cơ chế loại trùng và tổng hợp kết quả (Deduplication &amp; Synthesis):
+- Orchestrator chuẩn hóa tên đối thủ và domain để gộp các kết quả trùng lặp.
+- Sử dụng ma trận so sánh (Comparison Matrix) để tổng hợp thông tin; nếu hai worker phát hiện thông tin mâu thuẫn (ví dụ giá bán khác nhau), Orchestrator bảo toàn cả hai nguồn và ghi rõ sự sai lệch kèm mốc thời gian để người đọc đánh giá.
+4. Ngân sách, điều kiện dừng và xử lý lỗi:
+- Ngân sách cứng (Budget): Tối đa 50.000 token và thời gian timeout tối đa 90 giây cho toàn bộ phiên phân tích.
+- Điều kiện dừng: Hoàn tất thu thập đủ thông tin của top đối thủ HOẶC chạm ngưỡng ngân sách token/thời gian.
+- Xử lý lỗi: Nếu 1 worker bị lỗi timeout hoặc không tìm thấy nguồn, Orchestrator ghi nhận trạng thái 'Thiếu dữ liệu' cho đối thủ đó và tiếp tục tổng hợp các worker còn lại (Graceful Partial Degradation).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mẫu hình Orchestrator-Workers phân tán là giải pháp cho các bài toán phân tích mở không xác định trước số lượng. Thành công của mô hình nằm ở Hợp đồng giao tiếp có cấu trúc (Strict JSON Contracts), Cơ chế điều tiết lưu lượng (Throttling) và Dung sai lỗi từng phần (Partial Failure Tolerance).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents: Orchestrator-Workers Pattern (https://www.anthropic.com/research/building-effective-agents); OpenAI Swarm Multi-Agent Framework (https://github.com/openai/swarm)</t>
         </is>
       </c>
     </row>
@@ -1045,10 +1133,23 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm cả lỗi bùng nổ chi phí lẫn lỗi mất nguồn/mâu thuẫn; một câu trả lời chỉ nói 'giới hạn số worker' là chưa đủ.
-Phân tích theo nguyên lý thiết kế: Tìm cả lỗi bùng nổ chi phí lẫn lỗi mất nguồn/mâu thuẫn; một câu trả lời chỉ nói 'giới hạn số worker' là chưa đủ.</t>
+- Chỉ ra đủ 4 rủi ro thực tế (2.0 điểm): Nhận diện đúng bùng nổ chi phí/rate limit, rác nguồn, format bất đồng nhất và nối chuỗi nuốt mâu thuẫn.
+- Đề xuất 4 rào chắn bảo vệ tương ứng (2.0 điểm): Nêu rõ giới hạn worker song song, hợp đồng JSON bắt buộc, bộ tổng hợp loại trùng/bảo toàn mâu thuẫn và giới hạn ngân sách dừng cứng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Bốn rủi ro nghiêm trọng của thiết kế đề xuất ban đầu:
+- Rủi ro 1: Bùng nổ chi phí và nghẽn tài nguyên (Cost Explosion &amp; Rate Limiting): Khởi tạo đồng loạt 50 worker làm cạn kiệt ngân sách token và gây lỗi nghẽn hạn mức API (HTTP 429 Rate Limit Exceeded) từ nhà cung cấp LLM.
+- Rủi ro 2: Ô nhiễm dữ liệu và ảo giác không thể kiểm soát (Garbage Accumulation): Worker tự do tìm nguồn không có bộ lọc kiểm chứng, dễ thu thập thông tin rác, lỗi thời hoặc giả mạo từ Internet.
+- Rủi ro 3: Bất đồng nhất cấu trúc dữ liệu: Thiếu hợp đồng đầu ra chung khiến mỗi worker trả về một kiểu (JSON, Markdown, gạch đầu dòng), khiến bộ tổng hợp không thể phân tích và so sánh có ý nghĩa.
+- Rủi ro 4: Báo cáo hỗn độn, nuốt mâu thuẫn: Bộ tổng hợp chỉ 'nối chuỗi văn bản' (concatenation) sẽ tạo ra tài liệu dài dòng, trùng lặp hàng chục lần và triệt tiêu các mâu thuẫn dữ liệu quan trọng, khiến người ra quyết định bị hiểu lầm.
+2. Đề xuất các rào chắn kỹ thuật bảo vệ hệ thống:
+- Rào chắn số nhánh (Concurrency Throttling): Giới hạn tối đa 5-8 worker chạy song song; chia thành các đợt (batches) có điều tiết lưu lượng.
+- Rào chắn Hợp đồng đầu ra (Enforced Output Schema): Bắt buộc mọi worker phản hồi theo định dạng JSON Schema chuẩn gồm các trường: thực thể, luận điểm chính, số liệu và trích dẫn URL nguồn gốc có thể kiểm chứng.
+- Rào chắn Tổng hợp bằng chứng (Evidence Grounding &amp; Conflict Resolution): Bộ tổng hợp chạy thuật toán loại trùng (deduplication) và chủ động trích xuất các điểm mâu thuẫn giữa các nguồn ra một mục riêng 'Bất đồng quan điểm cần lưu ý'.
+- Rào chắn Điều kiện dừng &amp; Ngân sách (Hard Budget &amp; Termination): Đặt ngân sách tối đa 40.000 token và thời gian chạy tối đa 60 giây; nếu chạm ngưỡng, dừng sinh mới và tổng hợp ngay lập tức các dữ liệu đã thu thập được.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tác nhân tự trị không có rào chắn là công thức tạo ra thảm họa chi phí và dữ liệu rác. Một kiến trúc Multi-Agent sản xuất bắt buộc phải áp dụng nguyên tắc quản trị phân tán: Định mức tài nguyên (Resource Quotas), Ranh giới cấu trúc dữ liệu (Schema Boundaries) và Giải quyết xung đột thông tin (Conflict Transparency).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents: Evaluating Agent Architectures (https://www.anthropic.com/research/building-effective-agents); OWASP Top 10 for LLMs - LLM04: Model Denial of Service (https://owasp.org/www-project-top-10-for-large-language-model-applications/)</t>
         </is>
       </c>
     </row>
@@ -1132,10 +1233,33 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết tiêu chí đạt/không đạt có thể quan sát được và hành động sau khi không đạt.
-Phân tích theo nguyên lý thiết kế: Viết tiêu chí đạt/không đạt có thể quan sát được và hành động sau khi không đạt.</t>
+- Tiêu chí đánh giá khách quan, đo lường được (1.0 điểm): Định nghĩa rõ tiêu chí trích dẫn hợp lệ, tuân thủ chính sách và độ rõ ràng của ngôn ngữ.
+- Phản hồi có cấu trúc mang tính hành động (1.0 điểm): Thiết kế phản hồi JSON chỉ rõ câu vi phạm và hướng dẫn sửa cụ thể cho optimizer.
+- Điều kiện dừng và cơ chế ngắt mạch (1.0 điểm): Đặt điều kiện dừng khi pass 100% hoặc chạm ngưỡng tối đa 3 vòng lặp để escalate cho luật sư.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế vòng lặp Evaluator–Optimizer cho soạn thảo thư điện tử pháp lý:
+1. Bộ tiêu chí đánh giá có thể quan sát được (Evaluator Rubric Criteria):
+- Tiêu chí 1 (Tính hợp lệ của trích dẫn - Citation Validity): 100% điều khoản trích dẫn phải tồn tại chính xác trong văn bản luật/chính sách được cung cấp (kiểm tra regex số hiệu điều khoản và đối soát văn bản).
+- Tiêu chí 2 (Không hứa hẹn vượt chính sách - Policy Boundary Compliance): Email không được chứa các từ ngữ cam kết tuyệt đối, bảo đảm bồi thường ngoài phạm vi hoặc từ bỏ quyền miễn trừ trách nhiệm của công ty.
+- Tiêu chí 3 (Ngôn ngữ rõ ràng, chuẩn mực - Clarity &amp; Tone): Điểm độ đọc hiểu (Flesch-Kincaid / Readability) đạt chuẩn, cấu trúc đoạn mạch lạc, không dùng từ ngữ tối nghĩa.
+2. Cơ chế phản hồi có cấu trúc cho Optimizer (Structured Feedback Loop):
+Nếu Evaluator chấm 'Không đạt' ở bất kỳ tiêu chí nào, nó KHÔNG chỉ nói chung chung mà sinh ra phản hồi có cấu trúc JSON:
+```json
+{
+  "passed": false,
+  "violations": [
+    {"criterion": "Policy Boundary", "problematic_phrase": "Công ty sẽ đền bù toàn bộ chi phí", "instruction": "Sửa thành: Công ty sẽ hỗ trợ xem xét theo quy trình khiếu nại tại Điều 4"}
+  ]
+}
+```
+Optimizer nhận JSON này và thực hiện chỉnh sửa đúng các câu vi phạm.
+3. Điều kiện dừng an toàn (Termination Conditions):
+- Dừng thành công: Khi bài viết vượt qua 100% các tiêu chí kiểm tra (Passed == True).
+- Dừng thất bại (Circuit Breaker): Tối đa 3 vòng lặp (Max iterations = 3). Nếu sau 3 lần sửa vẫn không đạt chuẩn pháp lý, dừng vòng lặp tự động và chuyển email nháp kèm lịch sử phản hồi vi phạm cho Luật sư nội bộ xử lý thủ công.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mẫu hình Evaluator-Optimizer áp dụng cơ chế tự sửa lỗi có định hướng (Targeted Self-Correction). Evaluator đóng vai trò là một 'bộ lọc phê bình độc lập' đưa ra phản hồi mang tính hành động (Actionable Feedback). Bộ ngắt mạch (Circuit Breaker sau 3 lần) bảo vệ hệ thống khỏi vòng lặp vô tận gây lãng phí chi phí token.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents: Evaluator-Optimizer Workflow (https://www.anthropic.com/research/building-effective-agents); Madaan, A., et al. (2023). Self-Refine. NeurIPS 2023 (https://arxiv.org/abs/2303.17651)</t>
         </is>
       </c>
     </row>
@@ -1168,10 +1292,30 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi bước nào có thể đảo ngược và bước nào tạo ra phán đoán hoặc tác động bên ngoài.
-Phân tích theo nguyên lý thiết kế: Hỏi bước nào có thể đảo ngược và bước nào tạo ra phán đoán hoặc tác động bên ngoài.</t>
+- Phân bổ chính xác Automate và Augment cho 4 bước (1.5 điểm): Gán đúng Automate cho bước 1 &amp; 2; Gán Augment cho bước 3 &amp; 4.
+- Nêu rõ trách nhiệm và chỉ số đo lường riêng biệt (1.5 điểm): Nêu đủ trách nhiệm phân cấp và chỉ số đo lường tương ứng cho từng bước (Precision, Recall, Acceptance rate, CSAT).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân công vai trò Tự động hóa (Automate) và Hỗ trợ con người (Augment) trong quy trình xử lý khiếu nại y tế:
+1. Bước 1 (Trích mã hồ sơ bệnh án) -&gt; TỰ ĐỘNG HÓA (AUTOMATE):
+- Bản chất: Tác vụ trích xuất thực thể tất định (Regex / OCR NER), hoàn toàn có thể đảo ngược và không gây tác động bên ngoài.
+- Trách nhiệm: Hệ thống phần mềm chịu trách nhiệm tự động trích xuất.
+- Chỉ số đo lường: Tỷ lệ trích xuất mã chính xác (Extraction Accuracy / Precision &amp; Recall &gt;= 99%).
+2. Bước 2 (Gom tài liệu liên quan) -&gt; TỰ ĐỘNG HÓA (AUTOMATE):
+- Bản chất: Truy vấn và kết hợp dữ liệu có sẵn trong kho lưu trữ y tế (Database indexing &amp; Retrieval), không thay đổi trạng thái hồ sơ.
+- Trách nhiệm: Hệ thống RAG/Search chịu trách nhiệm tổng hợp đầy đủ tài liệu.
+- Chỉ số đo lường: Tỷ lệ thu hồi tài liệu liên quan (Document Retrieval Recall &gt;= 98%).
+3. Bước 3 (Đề xuất mức độ ưu tiên) -&gt; HỖ TRỢ CON NGƯỜI (AUGMENT):
+- Bản chất: Đòi hỏi phán đoán lâm sàng và phân loại tính cấp bách dựa trên tình trạng sức khỏe bệnh nhân; sai lệch có thể ảnh hưởng tính mạng.
+- Trách nhiệm: AI đề xuất mức ưu tiên kèm giải thích; Bác sĩ/Điều dưỡng trưởng rà soát và xác nhận mức ưu tiên chính thức.
+- Chỉ số đo lường: Tỷ lệ bác sĩ chấp thuận gợi ý của AI (Physician Recommendation Acceptance Rate).
+4. Bước 4 (Gửi quyết định cuối cho bệnh nhân) -&gt; HỖ TRỢ CON NGƯỜI / THỰC THI BỞI CON NGƯỜI (AUGMENT / HUMAN-IN-THE-LOOP):
+- Bản chất: Hành động tạo tác động ngoại vi vĩnh viễn (Irreversible external action), mang tính pháp lý y tế và ảnh hưởng tâm lý người bệnh.
+- Trách nhiệm: AI soạn sẵn bản thảo quyết định và tóm tắt chuyên môn; Lãnh đạo hội đồng chuyên môn ký duyệt và trực tiếp gửi cho bệnh nhân.
+- Chỉ số đo lường: Tỷ lệ khiếu nại tái diễn và mức độ hài lòng của bệnh nhân (Patient Satisfaction Score - CSAT).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc phân định ranh giới tự động hóa theo mức độ tác động và tính có thể đảo ngược: Tác vụ thu thập thông tin nội bộ (Reversible Internal Tasks) -&gt; Tự động hóa tối đa; Tác vụ phán đoán lâm sàng và hành động đối ngoại không thể đảo ngược (Irreversible High-Stakes Actions) -&gt; Bắt buộc giữ con người làm trung tâm quyết định (Human Agency).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Parasuraman, R., et al. (2000). A Model for Types and Levels of Human Interaction with Automation (https://ieeexplore.ieee.org/document/844357); WHO Guidance on AI in Health (https://www.who.int/publications/i/item/9789240029200)</t>
         </is>
       </c>
     </row>
@@ -1203,10 +1347,26 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng dùng ngưỡng tiền để thay cho kiểm soát; hãy hỏi bước nào có thể sửa lại và bước nào gây hậu quả không đảo ngược.
-Phân tích theo nguyên lý thiết kế: Đừng dùng ngưỡng tiền để thay cho kiểm soát; hãy hỏi bước nào có thể sửa lại và bước nào gây hậu quả không đảo ngược.</t>
+- Phản biện sâu sắc đề xuất cũ (1.0 điểm): Chỉ ra rủi ro nợ xấu khi tự duyệt 100 triệu, việc từ chối oan khi thiếu giấy tờ và vai trò bị động của nhân viên.
+- Viết lại phân công 4 bước chuẩn xác (1.0 điểm): Trích dữ liệu (auto), phát hiện thiếu (auto hỗ trợ bổ sung), đề xuất hạn mức (augment) và giải ngân (human gate).
+- Nêu điểm chặn bắt buộc và 3 chỉ số theo dõi (1.0 điểm): Nêu rõ chốt chặn chữ ký con người tại Core Banking và 3 chỉ số (nợ xấu, từ chối oan, tỷ lệ override).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phản biện đề xuất tự động hóa tín dụng ban đầu:
+Đề xuất trên cực kỳ nguy hiểm và thiếu trách nhiệm: (1) Ngưỡng 100 triệu là con số tài chính lớn, để mô hình tự động duyệt mà không có kiểm toán sẽ dẫn đến nguy cơ gian lận tín dụng có tổ chức và nợ xấu tăng vọt; (2) Tự động từ chối ngay khi thiếu giấy tờ mà không hướng dẫn bổ sung sẽ gây ức chế và đánh mất khách hàng tiềm năng; (3) Đẩy con người về thế bị động (chỉ xem khi khách khiếu nại) biến nhân viên thành người đi dập lửa hậu quả thay vì người kiểm soát rủi ro.
+2. Phân công lại theo 4 bước chuẩn mực:
+- Bước 1 (Trích dữ liệu) -&gt; TỰ ĐỘNG HÓA (AUTOMATE): AI đọc hồ sơ, trích xuất căn cước, sao kê thu nhập thành JSON chuẩn. Trách nhiệm: Hệ thống phần mềm.
+- Bước 2 (Phát hiện thiếu giấy tờ) -&gt; TỰ ĐỘNG HÓA KÈM HỖ TRỢ (AUTOMATE WITH USER LOOP): Hệ thống tự động kiểm tra đối chiếu danh mục giấy tờ. Nếu thiếu, tự động gửi thông báo thân thiện hướng dẫn khách nộp bổ sung trực tiếp, KHÔNG tự ý từ chối hồ sơ.
+- Bước 3 (Đề xuất hạn mức) -&gt; HỖ TRỢ CON NGƯỜI (AUGMENT): AI tính toán điểm tín dụng nội bộ và đề xuất hạn mức kèm bảng giải thích rủi ro. Trách nhiệm: Chuyên viên tín dụng thẩm định đề xuất.
+- Bước 4 (Quyết định giải ngân) -&gt; CON NGƯỜI GIỮ QUYỀN DUYỆT (HUMAN APPROVAL GATE): Bắt buộc phải có chữ ký số của Chuyên viên hoặc Trưởng phòng tín dụng trước khi lệnh giải ngân được gửi sang hệ thống Core Banking.
+3. Điểm chặn bắt buộc (Hard Gate): Cổng giải ngân tại Core Banking yêu cầu mã xác thực phê duyệt của con người, không chấp nhận lệnh gọi tự động từ dịch vụ AI.
+4. Ba chỉ số bắt buộc phải theo dõi:
+- Tỷ lệ nợ xấu (Non-Performing Loan Rate - NPL) của các hồ sơ được AI hỗ trợ.
+- Tỷ lệ từ chối sai lệch (False Rejection Rate) do lỗi trích xuất giấy tờ.
+- Tỷ lệ chuyên viên tín dụng ghi đè / bác bỏ gợi ý hạn mức của AI (Override Rate).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong các hệ thống tài chính tín dụng (Credit Underwriting), rủi ro đạo đức và rủi ro quy định (Regulatory Compliance) đòi hỏi sự phân định rạch ròi giữa 'Gợi ý tính toán' (Scoring Suggestion) và 'Quyền cam kết tài chính' (Financial Commitment). Một hạn mức 100 triệu giải ngân sai sẽ không thể thu hồi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Basel Committee on Banking Supervision - Credit Risk Management (https://www.bis.org/publ/bcbs75.htm); Federal Reserve SR 11-7: Model Risk Management (https://www.federalreserve.gov/supervisionreg/srletters/sr1107.htm)</t>
         </is>
       </c>
     </row>
@@ -1340,10 +1500,18 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chỉ hỏi trường còn trống trong dữ liệu định tuyến.
-Phân tích theo nguyên lý thiết kế: Chỉ hỏi trường còn trống trong dữ liệu định tuyến.</t>
+- Câu hỏi làm rõ chuẩn xác, ngắn gọn (2.0 điểm): Đặt đúng câu hỏi chọn giữa khung giờ 13–16h hay 16–19h mà không hỏi lại các thông tin đã biết.
+- Giải thích nguyên lý thiết kế hội thoại (1.0 điểm): Giải thích việc chỉ hỏi trường còn trống và đưa ra lựa chọn đóng để giảm tải nhận thức cho người dùng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Câu hỏi làm rõ ngắn nhất và chuẩn xác nhất để chọn nhánh tìm vé:
+"Bạn muốn khởi hành vào đầu giờ chiều (13h – 16h) hay cuối giờ chiều (16h – 19h)?"
+Giải thích thiết kế giao diện hội thoại (Conversational UX Rationale):
+- Hệ thống đã biết đầy đủ các thông tin: Điểm đi, Điểm đến, Ngày khởi hành (chiều mai) và Ngân sách tối đa (2 triệu đồng). Do đó, tuyệt đối KHÔNG hỏi lại những thông tin người dùng đã cung cấp.
+- Trường dữ liệu duy nhất còn thiếu để định tuyến chính xác giữa hai nhánh tìm kiếm là Khung giờ khởi hành cụ thể trong buổi chiều. Câu hỏi được thiết kế ngắn gọn, trực diện, đưa ra sẵn hai lựa chọn đóng (closed choices: 13h-16h vs 16h-19h) giúp người dùng có thể nhấp chọn ngay với một thao tác chạm mà không cần phải gõ lại văn bản dài dòng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc 'Minimal Cognitive Load &amp; Non-redundancy' trong thiết kế hội thoại AI: Chỉ làm rõ trường dữ liệu còn thiếu cuối cùng ngăn cản việc kích hoạt nhánh nghiệp vụ. Đưa ra các tùy chọn phân nhánh cụ thể thay vì đặt câu hỏi mở mơ hồ giúp tối ưu tỷ lệ chuyển đổi tác vụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Conversational AI Design Guidelines - Asking Clarifying Questions (https://developers.google.com/assistant/conversation-design); Nielsen Norman Group - Chatbot UX (https://www.nngroup.com/articles/chatbots/)</t>
         </is>
       </c>
     </row>
@@ -1378,10 +1546,19 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm trường nào còn trống trong dữ liệu gửi.
-Phân tích theo nguyên lý thiết kế: Tìm trường nào còn trống trong dữ liệu gửi.</t>
+- Câu hỏi làm rõ đủ 2 thông tin thiếu (1.5 điểm): Hỏi rõ nhóm nhận cụ thể và trạng thái gửi bản nháp hay bản chính thức.
+- Điều kiện tiên quyết để tiếp tục (1.5 điểm): Định nghĩa rõ các điều kiện về xác thực nhóm nhận hợp lệ, xác định cờ phiên bản và cổng xác nhận preview của người dùng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Câu hỏi làm rõ chuẩn xác dành cho người dùng:
+"Bạn muốn gửi [Tên tệp báo cáo] tới nhóm nào (ví dụ: Nhóm Dự án, Nhóm Kinh doanh hay Ban Giám đốc), và bạn muốn gửi dưới dạng Bản nháp để góp ý hay Bản chính thức phê duyệt?"
+2. Điều kiện bắt buộc để tiếp tục thực thi hành động gửi (Gating Conditions):
+- Điều kiện 1 (Đầy đủ người nhận): Trường `recipient_group_id` được xác định chính xác và tương ứng với một nhóm có thật trong danh bạ phân quyền của tổ chức.
+- Điều kiện 2 (Xác nhận trạng thái tài liệu): Người dùng xác nhận rõ ràng giá trị cờ `is_final_version` (True nếu là bản chính thức, False nếu là bản nháp).
+- Điều kiện 3 (Xác nhận trước khi gửi đối ngoại - Pre-send Confirmation): Nếu là bản chính thức hoặc gửi cho nhóm đối tác/lãnh đạo, hệ thống phải hiển thị một hộp thoại tóm tắt (Preview Modal) kèm nút 'Xác nhận gửi' để người dùng kiểm tra lại lần cuối trước khi file được phát đi.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc 'Defensive Dispatching' trong tương tác người-máy. Gửi tài liệu là hành động đối ngoại không thể thu hồi hoàn toàn. Việc thiếu đối tượng nhận và trạng thái tài liệu là rủi ro rò rỉ thông tin nghiêm trọng; hệ thống bắt buộc phải dừng lại ở cổng làm rõ trước khi thực thi lệnh phát tán tài liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Microsoft HAX Toolkit - Guideline 10: Scope of Action (https://www.microsoft.com/en-us/haxtoolkit/); Nielsen Norman Group - Confirmation Dialogs (https://www.nngroup.com/articles/confirmation-dialog/)</t>
         </is>
       </c>
     </row>
